--- a/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>BKKLY</t>
   </si>
@@ -656,56 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -733,8 +736,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -791,8 +800,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -804,8 +816,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,8 +878,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,8 +910,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -920,8 +942,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -930,8 +955,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -959,8 +985,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -988,8 +1017,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1001,8 +1033,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1030,8 +1063,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1059,8 +1095,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1088,8 +1127,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1117,8 +1159,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1146,8 +1191,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1204,8 +1255,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,8 +1287,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,8 +1319,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1291,8 +1351,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1320,8 +1383,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1349,8 +1415,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1378,8 +1447,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1407,8 +1479,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1436,8 +1511,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1465,42 +1543,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1512,8 +1596,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,66 +1610,73 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1379900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1294000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1053000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1144500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1324000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1094200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1210900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1369500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2999100</v>
+      </c>
+      <c r="E42" s="3">
         <v>7596900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2832300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3050200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2474800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2995600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2639200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2266800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2602900</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1612,182 +1704,203 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>237900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>313000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>341100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>234200</v>
+      </c>
+      <c r="E45" s="3">
         <v>509600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>272800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>612800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>364500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>703200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>322000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>765400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4777600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9400600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4396000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4807600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4476300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4792900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4513200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4401800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4760600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>53409100</v>
+      </c>
+      <c r="E47" s="3">
         <v>50961500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47689300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48119200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>52512000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47540800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49214200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>52596200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48816600</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1750900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1875300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1691200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1707600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1801300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1726000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1785900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1806600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1790400</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>809900</v>
+      </c>
+      <c r="E49" s="3">
         <v>949200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>919400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>939500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>966200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>967200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1002700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1005700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1815,8 +1928,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1844,37 +1960,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1022800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1497500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1453700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1465800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1063100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1901900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1094700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>783700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>808400</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1902,37 +2024,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>132604400</v>
+      </c>
+      <c r="E54" s="3">
         <v>138386900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123316900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125486400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>131315200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>124700800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>127021100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>130963400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>127910900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +2072,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1957,182 +2086,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>93925500</v>
+      </c>
+      <c r="E57" s="3">
         <v>96171100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87779400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>88074400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>93829500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>86521100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>91812500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94116600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94581700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2659300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2255500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2595200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2429500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2481300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2958000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3546000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1760100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2589700</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8359800</v>
+      </c>
+      <c r="E59" s="3">
         <v>223200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>221000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>212800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>176300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6922000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>228600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5763100</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105669200</v>
+      </c>
+      <c r="E60" s="3">
         <v>98653600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>91368200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90718400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>104893500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>89656900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>103051300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96106900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103527700</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5454400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6401600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5536400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5579700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5545800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6656600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4331200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5452800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4910700</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4817600</v>
+      </c>
+      <c r="E62" s="3">
         <v>16305200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11112600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13832300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5012900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13889300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4429600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14217500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4381000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2160,8 +2308,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2340,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2218,37 +2372,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>116379900</v>
+      </c>
+      <c r="E66" s="3">
         <v>121360600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108421000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110132100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>115874600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110205800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>112224700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>115781600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113240500</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2260,8 +2420,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2289,8 +2450,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2318,8 +2482,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2347,8 +2514,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2376,37 +2546,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12862900</v>
+      </c>
+      <c r="E72" s="3">
         <v>13317000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11483800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11548900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11904600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10932500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11097500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11338500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10867200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2434,8 +2610,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2463,8 +2642,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2492,37 +2674,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16171100</v>
+      </c>
+      <c r="E76" s="3">
         <v>16971500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14844600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15299000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15386600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14444800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14742400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15124700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14618500</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2550,42 +2738,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2807,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2626,37 +2823,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E83" s="3">
         <v>34500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>43200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2684,8 +2885,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2713,8 +2917,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2742,8 +2949,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2771,8 +2981,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2800,37 +3013,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3207000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3100800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>536400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1057500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>334300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1367800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>556000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1689600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1107500</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2842,37 +3061,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2900,8 +3123,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2929,37 +3155,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1640700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>28200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-944400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-245700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1566800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-321200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1704500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2971,37 +3203,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>118000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>259800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>104400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>162100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3029,8 +3265,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3058,8 +3297,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3087,91 +3329,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1726400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-643600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-224000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>73800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>122900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-346000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-153800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1298500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-600</v>
       </c>
       <c r="K101" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>160800</v>
+      </c>
+      <c r="E102" s="3">
         <v>97800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-78400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-108900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>160400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-110100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-169700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>246000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>BKKLY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,72 +1696,79 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1296600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1379900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1294000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1053000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1144500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1324000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1094200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1210900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1369500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5396800</v>
+      </c>
+      <c r="E42" s="3">
         <v>2999100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7596900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2832300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3050200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2474800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2995600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2639200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2266800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2602900</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1707,200 +1799,221 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3">
         <v>164300</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
         <v>237900</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
         <v>313000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>341100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E45" s="3">
         <v>234200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>509600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>272800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>612800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>364500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>703200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>322000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>765400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6857100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4777600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9400600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4396000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4807600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4476300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4792900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4513200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4401800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4760600</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>53323500</v>
+      </c>
+      <c r="E47" s="3">
         <v>53409100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50961500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47689300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>48119200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52512000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47540800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49214200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>52596200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>48816600</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1745700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1750900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1875300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1691200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1707600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1801300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1726000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1785900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1806600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1790400</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>789300</v>
+      </c>
+      <c r="E49" s="3">
         <v>809900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>949200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>919400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>939500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>966200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>967200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1002700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1005700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1118700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1022800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1497500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1453700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1465800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1063100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1901900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1094700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>783700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>808400</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>136293100</v>
+      </c>
+      <c r="E54" s="3">
         <v>132604400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>138386900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123316900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125486400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131315200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>124700800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>127021100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>130963400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>127910900</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,200 +2216,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>94971300</v>
+      </c>
+      <c r="E57" s="3">
         <v>93925500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>96171100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87779400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>88074400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>93829500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>86521100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>91812500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94116600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94581700</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1749000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2659300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2255500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2595200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2429500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2481300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2958000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3546000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1760100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2589700</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E59" s="3">
         <v>8359800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>223200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>221000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>212800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>176300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6922000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>228600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5763100</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96942900</v>
+      </c>
+      <c r="E60" s="3">
         <v>105669200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98653600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91368200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90718400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>104893500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89656900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103051300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>96106900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>103527700</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7341700</v>
+      </c>
+      <c r="E61" s="3">
         <v>5454400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6401600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5536400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5579700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5545800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6656600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4331200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5452800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4910700</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15364400</v>
+      </c>
+      <c r="E62" s="3">
         <v>4817600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16305200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11112600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13832300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5012900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13889300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4429600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14217500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4381000</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>119649000</v>
+      </c>
+      <c r="E66" s="3">
         <v>116379900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>121360600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108421000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>110132100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>115874600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110205800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>112224700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>115781600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113240500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13380000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12862900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13317000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11483800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11548900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11904600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10932500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11097500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11338500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10867200</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16588400</v>
+      </c>
+      <c r="E76" s="3">
         <v>16171100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16971500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14844600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15299000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15386600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14444800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14742400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15124700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14618500</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,40 +3021,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E83" s="3">
         <v>18900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,40 +3229,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3207000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3100800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>536400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1057500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>334300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1367800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>556000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1689600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1107500</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,40 +3281,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,40 +3384,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>1640700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>28200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-944400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-245700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1566800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-321200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1704500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,40 +3436,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>118000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>259800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>104400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>162100</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,100 +3574,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>1726400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-643600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-224000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>73800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>122900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-346000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-153800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1298500</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-600</v>
       </c>
       <c r="L101" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>160800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-108900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>160400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-110100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-169700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>246000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>BKKLY</t>
   </si>
@@ -656,62 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +749,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,8 +787,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -815,8 +825,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +843,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +879,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,8 +917,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -935,8 +955,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -970,8 +993,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,8 +1008,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1017,8 +1044,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1052,8 +1082,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,8 +1100,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1102,8 +1136,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1137,8 +1174,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,8 +1212,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1207,8 +1250,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,8 +1288,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,8 +1326,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1312,8 +1364,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1347,8 +1402,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,8 +1440,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1417,8 +1478,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1516,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,8 +1554,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1522,8 +1592,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1557,8 +1630,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,8 +1668,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1627,48 +1706,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1767,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,78 +1783,85 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
         <v>1296600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1379900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1294000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1053000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1144500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1324000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1094200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1210900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1369500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5396800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>2657300</v>
+      </c>
+      <c r="F42" s="3">
         <v>2999100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7596900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2832300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3050200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2474800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2995600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2639200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2266800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2602900</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1802,218 +1895,239 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>164300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>237900</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>313000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>341100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>163700</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
+        <v>352000</v>
+      </c>
+      <c r="F45" s="3">
         <v>234200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>509600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>272800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>612800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>364500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>703200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>322000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>765400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>6857100</v>
+      <c r="D46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E46" s="3">
+        <v>4305900</v>
+      </c>
+      <c r="F46" s="3">
         <v>4777600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9400600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4396000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4807600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4476300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4792900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4513200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4401800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4760600</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>53323500</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E47" s="3">
+        <v>56062900</v>
+      </c>
+      <c r="F47" s="3">
         <v>53409100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50961500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>47689300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>48119200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>52512000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47540800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>49214200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>52596200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>48816600</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>1745700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1750900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1875300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1691200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1707600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1801300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1726000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1785900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1806600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1790400</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3">
         <v>789300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>809900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>949200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>919400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>939500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>966200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>967200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1002700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1005700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2161,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2199,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>1118700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1022800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1497500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1453700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1465800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1063100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1901900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1094700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>783700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>808400</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2275,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3">
         <v>136293100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>132604400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>138386900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>123316900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>125486400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>131315200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124700800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>127021100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>130963400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127910900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2331,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,218 +2347,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
         <v>94971300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>93925500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96171100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>87779400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88074400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>93829500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>86521100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>91812500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94116600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94581700</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3">
         <v>1749000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2659300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2255500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2595200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2429500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2481300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2958000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3546000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1760100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2589700</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>222600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8359800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>223200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>221000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>212800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7800300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>176300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6922000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>228600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5763100</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>96942900</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E60" s="3">
+        <v>96945000</v>
+      </c>
+      <c r="F60" s="3">
         <v>105669200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98653600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91368200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90718400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>104893500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>89656900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103051300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>96106900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>103527700</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>7341700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5454400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6401600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5536400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5579700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5545800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6656600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4331200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5452800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4910700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>15364400</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
+        <v>15362300</v>
+      </c>
+      <c r="F62" s="3">
         <v>4817600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16305200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11112600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13832300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5012900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13889300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4429600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14217500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4381000</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2611,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2649,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2687,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
         <v>119649000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>116379900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>121360600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>108421000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110132100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>115874600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>110205800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112224700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>115781600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>113240500</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2743,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2779,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2817,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +2855,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +2893,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>13380000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12862900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13317000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11483800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11548900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11904600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10932500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11097500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11338500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10867200</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +2969,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3007,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3045,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3">
         <v>16588400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16171100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16971500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14844600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15299000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15386600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14444800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14742400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15124700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14618500</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,48 +3121,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3007,8 +3202,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3220,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>36200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>34700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>43200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3294,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3332,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3370,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3408,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,8 +3446,11 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3241,34 +3458,37 @@
         <v>4</v>
       </c>
       <c r="E89" s="3">
+        <v>-1898300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3207000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3100800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>536400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1057500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>334300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1367800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>556000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1689600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1107500</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,8 +3502,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3291,34 +3512,37 @@
         <v>4</v>
       </c>
       <c r="E91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-17200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-39600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3576,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,8 +3614,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3396,34 +3626,37 @@
         <v>4</v>
       </c>
       <c r="E94" s="3">
+        <v>-826100</v>
+      </c>
+      <c r="F94" s="3">
         <v>1640700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>28200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-944400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-245700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1566800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-321200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1704500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3670,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>118000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>259800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>104400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>162100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3744,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +3782,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,8 +3820,11 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3586,69 +3832,75 @@
         <v>4</v>
       </c>
       <c r="E100" s="3">
+        <v>2624900</v>
+      </c>
+      <c r="F100" s="3">
         <v>1726400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-643600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-224000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>73800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>122900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-346000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1298500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-600</v>
       </c>
       <c r="M101" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3656,30 +3908,33 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="F102" s="3">
         <v>160800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-78400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-108900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>160400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-75500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-110100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-169700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>246000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
   <si>
     <t>BKKLY</t>
   </si>
@@ -656,68 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +760,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +804,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +848,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +868,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +910,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +954,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +998,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1042,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1059,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1101,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1145,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1165,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1207,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1251,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1295,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1339,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1383,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1427,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1471,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1515,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1559,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1603,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1647,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1691,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1735,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1779,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +1823,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +1867,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +1936,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,90 +1954,97 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1508100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1175600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1166800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1296600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1379900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1294000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1053000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1144500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1324000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1094200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1210900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1369500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3551800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3221400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3234300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2657300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2999100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7596900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2832300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3050200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2474800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2995600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2639200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2266800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2602900</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1992,13 +2084,16 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
+      <c r="D44" s="3">
+        <v>162600</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -2006,240 +2101,258 @@
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>164300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>237900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>313000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>341100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>173400</v>
+      </c>
+      <c r="E45" s="3">
         <v>358900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>829500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>352000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>234200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>509600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>272800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>612800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>364500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>703200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>322000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>765400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5395900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4755900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4761700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4305900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4777600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9400600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4396000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4807600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4476300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4792900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4513200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4401800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4760600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62508800</v>
+      </c>
+      <c r="E47" s="3">
         <v>59220400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>57965500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>56062900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>53409100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50961500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47689300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48119200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>52512000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47540800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>49214200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>52596200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>48816600</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2267200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2237400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2265300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1745700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1750900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1875300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1691200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1707600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1801300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1726000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1785900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1806600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1790400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>714000</v>
+      </c>
+      <c r="E49" s="3">
         <v>759300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>797100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>789300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>809900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>949200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>919400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>939500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>966200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>967200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1002700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1005700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2392,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2436,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1141900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1120100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1118700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1022800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1497500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1453700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1465800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1063100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1901900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1094700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>783700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>808400</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2524,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>146061500</v>
+      </c>
+      <c r="E54" s="3">
         <v>139756600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>141936800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>136293100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>132604400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>138386900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>123316900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>125486400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>131315200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124700800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127021100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>130963400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>127910900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2588,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2606,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>103203400</v>
+      </c>
+      <c r="E57" s="3">
         <v>97748600</v>
       </c>
-      <c r="E57" s="3">
-        <v>99885400</v>
-      </c>
       <c r="F57" s="3">
+        <v>98404700</v>
+      </c>
+      <c r="G57" s="3">
         <v>94971300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>93925500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>96171100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>87779400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>88074400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>93829500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>86521100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91812500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>94116600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94581700</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2109800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1879000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2893100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1749000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2659300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2255500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2595200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2429500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2481300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2958000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3546000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1760100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2589700</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7916100</v>
+      </c>
+      <c r="E59" s="3">
         <v>177700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>208000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>222600</v>
       </c>
-      <c r="G59" s="3">
-        <v>8359800</v>
-      </c>
       <c r="H59" s="3">
+        <v>8360300</v>
+      </c>
+      <c r="I59" s="3">
         <v>223200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>221000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>212800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7800300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>176300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6922000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>228600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5763100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>114172200</v>
+      </c>
+      <c r="E60" s="3">
         <v>99807400</v>
       </c>
-      <c r="E60" s="3">
-        <v>103752700</v>
-      </c>
       <c r="F60" s="3">
+        <v>102272000</v>
+      </c>
+      <c r="G60" s="3">
         <v>96945000</v>
       </c>
-      <c r="G60" s="3">
-        <v>105669200</v>
-      </c>
       <c r="H60" s="3">
+        <v>105669700</v>
+      </c>
+      <c r="I60" s="3">
         <v>98653600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>91368200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90718400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>104893500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>89656900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>103051300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96106900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103527700</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6595900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6613400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7341700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5454400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6401600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5536400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5579700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5545800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6656600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4331200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5452800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4910700</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5404200</v>
+      </c>
+      <c r="E62" s="3">
         <v>15297700</v>
       </c>
-      <c r="E62" s="3">
-        <v>13399800</v>
-      </c>
       <c r="F62" s="3">
+        <v>14880500</v>
+      </c>
+      <c r="G62" s="3">
         <v>15362300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4817600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16305200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11112600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13832300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5012900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13889300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4429600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14217500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4381000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +2912,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +2956,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3000,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127807300</v>
+      </c>
+      <c r="E66" s="3">
         <v>121702800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>124238400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>119649000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>116379900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>121360600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108421000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>110132100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>115874600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>110205800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112224700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>115781600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>113240500</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3064,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3106,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3150,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3194,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3238,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14933200</v>
+      </c>
+      <c r="E72" s="3">
         <v>14260500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13975400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13380000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12862900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13317000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11483800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11548900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11904600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10932500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11097500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11338500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10867200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3326,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3370,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3414,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18198400</v>
+      </c>
+      <c r="E76" s="3">
         <v>18001200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17644200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16588400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16171100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16971500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14844600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15299000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15386600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14444800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14742400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15124700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14618500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +3502,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +3595,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +3615,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E83" s="3">
         <v>44500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +3701,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +3745,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +3789,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +3833,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +3877,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-449000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5971900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-757400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1898300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-3207000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3194800</v>
+      </c>
+      <c r="I89" s="3">
         <v>3100800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>536400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1057500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>334300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1367800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>556000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1689600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1107500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,49 +3941,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4027,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4071,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1056200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4425400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1867400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-826100</v>
       </c>
-      <c r="G94" s="3">
-        <v>1640700</v>
-      </c>
       <c r="H94" s="3">
+        <v>1628500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>28200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-944400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-245700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1566800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-321200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1704500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4135,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>117600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>382000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>118000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>259800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>104400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>162100</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4221,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4265,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,127 +4309,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1803900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1537400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1298700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2624900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1726400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-643600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-224000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>73800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>122900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-346000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-153800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1298500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-600</v>
       </c>
       <c r="O101" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E102" s="3">
         <v>8700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-188900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-98100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>160800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>97800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-78400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-108900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>160400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-110100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-169700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>246000</v>
       </c>
     </row>
